--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14660" windowHeight="13660"/>
+    <workbookView windowWidth="19240" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
     <t>bgm_02</t>
   </si>
   <si>
-    <t>这就是首座因元素污染失控而被废弃的 REC-006 基地，除了那些 【蚀源虫】，这里的反动分子也没少下功夫啊。</t>
+    <t>这就是首座因元素污染失控而被废弃的 REC-006 基地，除了那些 &lt;b&gt;【蚀源虫】&lt;/b&gt;，这里的反动分子也没少下功夫啊。</t>
   </si>
   <si>
     <t>主城拼命想要掩盖的罪恶与冲突，在这片荒原上却一览无余。没记错的话，当年是反动派的手笔，才酿成了这里的悲剧？</t>
@@ -155,6 +155,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">按 </t>
     </r>
     <r>
@@ -202,6 +209,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">按 </t>
     </r>
     <r>
@@ -265,6 +279,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>等等......元素能量的波动吸引了周围的&lt;b&gt;</t>
     </r>
     <r>
@@ -294,6 +315,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD83931"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>&lt;b&gt;&lt;color=#FF0000&gt;【</t>
     </r>
     <r>
@@ -378,6 +406,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>试着把&lt;b&gt;</t>
     </r>
     <r>
@@ -508,6 +543,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>你从那些虫子身上捡了什么东西回来？——啊，是&lt;b&gt;&lt;color=#FF0000&gt;</t>
     </r>
     <r>
@@ -537,6 +579,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>但你的储物器真得升升级了，&lt;b&gt;&lt;color=#FF0000&gt;</t>
     </r>
     <r>
@@ -575,6 +624,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>击败&lt;b&gt;</t>
     </r>
     <r>
@@ -641,14 +697,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“哔——”</t>
+      <t>“哔——”&lt;i&gt;&lt;color=#808080&gt;</t>
     </r>
     <r>
       <rPr>
@@ -659,7 +708,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>（*信号被紧急掐断）</t>
+      <t>（*信号被紧急掐断）&lt;/color&gt;&lt;/i&gt;</t>
     </r>
   </si>
   <si>
@@ -721,6 +770,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>  </t>
     </r>
     <r>
@@ -760,6 +816,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>    </t>
     </r>
     <r>
@@ -799,6 +862,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>   </t>
     </r>
     <r>
@@ -1064,6 +1134,15 @@
     </font>
     <font>
       <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1074,15 +1153,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFD83931"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19240" windowHeight="13660"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <t>絮</t>
   </si>
   <si>
-    <t>bgm_02</t>
+    <t>升华bgm</t>
   </si>
   <si>
     <t>这就是首座因元素污染失控而被废弃的 REC-006 基地，除了那些 &lt;b&gt;【蚀源虫】&lt;/b&gt;，这里的反动分子也没少下功夫啊。</t>
@@ -275,7 +275,7 @@
     <t>催化发射器运行正常，开了个好头。</t>
   </si>
   <si>
-    <t>bgm_01_main</t>
+    <t>主题bgm</t>
   </si>
   <si>
     <r>
@@ -697,6 +697,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>“哔——”&lt;i&gt;&lt;color=#808080&gt;</t>
     </r>
     <r>
@@ -1144,7 +1151,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFD83931"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1152,7 +1159,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFD83931"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1616,7 +1623,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1630,6 +1637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1951,11 +1959,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F118"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="7.96153846153846" customWidth="1"/>
-    <col min="3" max="3" width="11.8076923076923" customWidth="1"/>
-    <col min="4" max="4" width="15.9423076923077" customWidth="1"/>
+    <col min="2" max="2" width="7.96363636363636" customWidth="1"/>
+    <col min="3" max="3" width="11.8090909090909" customWidth="1"/>
+    <col min="4" max="4" width="15.9454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2049,10 +2057,10 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2088,7 +2096,7 @@
       <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2124,7 +2132,7 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2142,7 +2150,7 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2160,7 +2168,7 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2236,7 +2244,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="2:6">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2300,7 +2308,7 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2317,7 +2325,7 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2338,7 +2346,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="2:6">
+    <row r="22" spans="2:6">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2351,11 +2359,11 @@
       <c r="E22" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="2:6">
+    <row r="23" spans="2:6">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2368,7 +2376,7 @@
       <c r="E23" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="6" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2389,7 +2397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" ht="17" spans="2:6">
+    <row r="25" spans="2:6">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2399,10 +2407,10 @@
       <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2423,7 +2431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" ht="17" spans="2:6">
+    <row r="27" spans="2:6">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2436,7 +2444,7 @@
       <c r="E27" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2487,7 +2495,7 @@
       <c r="E30" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="6" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2504,7 +2512,7 @@
       <c r="E31" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2521,7 +2529,7 @@
       <c r="E32" t="s">
         <v>18</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="6" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2538,7 +2546,7 @@
       <c r="E33" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="6" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2555,7 +2563,7 @@
       <c r="E34" t="s">
         <v>18</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2593,7 +2601,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" ht="17" spans="2:6">
+    <row r="37" spans="2:6">
       <c r="B37" s="4">
         <v>33</v>
       </c>
@@ -2606,7 +2614,7 @@
       <c r="E37" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="6" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2627,7 +2635,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" ht="17" spans="2:6">
+    <row r="39" spans="2:6">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -2640,7 +2648,7 @@
       <c r="E39" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="6" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2797,7 +2805,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" ht="17" spans="2:6">
+    <row r="49" spans="2:6">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -2810,7 +2818,7 @@
       <c r="E49" t="s">
         <v>18</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2831,7 +2839,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" ht="17" spans="2:6">
+    <row r="51" spans="2:6">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -2844,7 +2852,7 @@
       <c r="E51" t="s">
         <v>18</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2912,11 +2920,11 @@
       <c r="E55" t="s">
         <v>18</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="56" ht="17" spans="2:6">
+    <row r="56" spans="2:6">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -2929,7 +2937,7 @@
       <c r="E56" t="s">
         <v>18</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3018,7 +3026,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" ht="17" spans="2:6">
+    <row r="62" spans="2:6">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -3031,7 +3039,7 @@
       <c r="E62" t="s">
         <v>18</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="6" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3188,7 +3196,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" ht="17" spans="2:6">
+    <row r="72" spans="2:6">
       <c r="B72" s="4">
         <v>68</v>
       </c>
@@ -3201,7 +3209,7 @@
       <c r="E72" t="s">
         <v>18</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="6" t="s">
         <v>91</v>
       </c>
     </row>
@@ -3218,11 +3226,11 @@
       <c r="E73" t="s">
         <v>18</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="F73" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="74" ht="17" spans="2:6">
+    <row r="74" spans="2:6">
       <c r="B74" s="4">
         <v>70</v>
       </c>
@@ -3235,11 +3243,11 @@
       <c r="E74" t="s">
         <v>18</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="75" ht="17" spans="2:6">
+    <row r="75" spans="2:6">
       <c r="B75" s="4">
         <v>71</v>
       </c>
@@ -3252,11 +3260,11 @@
       <c r="E75" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="76" ht="17" spans="2:6">
+    <row r="76" spans="2:6">
       <c r="B76" s="4">
         <v>72</v>
       </c>
@@ -3269,7 +3277,7 @@
       <c r="E76" t="s">
         <v>18</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="6" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3436,7 +3444,7 @@
       <c r="D86" t="s">
         <v>79</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F86" t="s">
@@ -3511,22 +3519,22 @@
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="2:6">
+    <row r="91" spans="3:3">
       <c r="C91" s="4"/>
     </row>
-    <row r="92" spans="2:6">
+    <row r="92" spans="3:3">
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="2:6">
+    <row r="93" spans="3:3">
       <c r="C93" s="4"/>
     </row>
-    <row r="94" spans="2:6">
+    <row r="94" spans="3:3">
       <c r="C94" s="4"/>
     </row>
-    <row r="95" spans="2:6">
+    <row r="95" spans="3:3">
       <c r="C95" s="4"/>
     </row>
-    <row r="96" spans="2:6">
+    <row r="96" spans="2:2">
       <c r="B96" s="4"/>
     </row>
     <row r="97" spans="2:2">
@@ -3577,24 +3585,24 @@
     <row r="112" spans="2:2">
       <c r="B112" s="4"/>
     </row>
-    <row r="113" spans="2:6">
+    <row r="113" spans="2:2">
       <c r="B113" s="4"/>
     </row>
-    <row r="114" spans="2:6">
+    <row r="114" spans="2:2">
       <c r="B114" s="4"/>
     </row>
-    <row r="115" spans="2:6">
+    <row r="115" spans="2:2">
       <c r="B115" s="4"/>
     </row>
-    <row r="116" spans="2:6">
+    <row r="116" spans="2:2">
       <c r="B116" s="4"/>
     </row>
-    <row r="117" spans="2:6">
+    <row r="117" spans="2:2">
       <c r="B117" s="4"/>
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="4"/>
-      <c r="F118" s="5"/>
+      <c r="F118" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3607,7 +3615,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3619,7 +3627,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="109">
   <si>
     <t>##var</t>
   </si>
@@ -273,9 +273,6 @@
   </si>
   <si>
     <t>催化发射器运行正常，开了个好头。</t>
-  </si>
-  <si>
-    <t>主题bgm</t>
   </si>
   <si>
     <r>
@@ -1141,7 +1138,6 @@
     </font>
     <font>
       <b/>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1158,6 +1154,7 @@
     </font>
     <font>
       <b/>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -2407,11 +2404,11 @@
       <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -2428,7 +2425,7 @@
         <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -2445,7 +2442,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="2:6">
@@ -2458,11 +2455,11 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" t="s">
-        <v>18</v>
+      <c r="E28" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -2479,7 +2476,7 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -2496,7 +2493,7 @@
         <v>18</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -2513,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -2530,7 +2527,7 @@
         <v>18</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="2:6">
@@ -2547,7 +2544,7 @@
         <v>18</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="2:6">
@@ -2564,7 +2561,7 @@
         <v>18</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -2577,11 +2574,11 @@
       <c r="D35" t="s">
         <v>20</v>
       </c>
-      <c r="E35" t="s">
-        <v>18</v>
+      <c r="E35" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -2598,7 +2595,7 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="2:6">
@@ -2615,7 +2612,7 @@
         <v>18</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -2632,7 +2629,7 @@
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="2:6">
@@ -2649,7 +2646,7 @@
         <v>18</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -2662,11 +2659,11 @@
       <c r="D40" t="s">
         <v>20</v>
       </c>
-      <c r="E40" t="s">
-        <v>18</v>
+      <c r="E40" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="2:6">
@@ -2683,7 +2680,7 @@
         <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="2:6">
@@ -2700,7 +2697,7 @@
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -2717,7 +2714,7 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="2:6">
@@ -2734,7 +2731,7 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="2:6">
@@ -2751,7 +2748,7 @@
         <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="2:6">
@@ -2768,7 +2765,7 @@
         <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -2785,7 +2782,7 @@
         <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -2802,7 +2799,7 @@
         <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -2819,7 +2816,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="2:6">
@@ -2836,7 +2833,7 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -2853,7 +2850,7 @@
         <v>18</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="2:6">
@@ -2870,7 +2867,7 @@
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="2:6">
@@ -2887,7 +2884,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="2:6">
@@ -2904,7 +2901,7 @@
         <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="2:6">
@@ -2921,7 +2918,7 @@
         <v>18</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="2:6">
@@ -2938,7 +2935,7 @@
         <v>18</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="2:6">
@@ -2955,7 +2952,7 @@
         <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="2:6">
@@ -2972,7 +2969,7 @@
         <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2983,13 +2980,13 @@
         <v>5001</v>
       </c>
       <c r="D59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
         <v>79</v>
-      </c>
-      <c r="E59" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="60" spans="2:6">
@@ -3000,13 +2997,13 @@
         <v>5001</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -3017,13 +3014,13 @@
         <v>5001</v>
       </c>
       <c r="D61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -3034,13 +3031,13 @@
         <v>5001</v>
       </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="2:6">
@@ -3057,7 +3054,7 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -3074,7 +3071,7 @@
         <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -3091,7 +3088,7 @@
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -3108,7 +3105,7 @@
         <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="2:6">
@@ -3125,7 +3122,7 @@
         <v>18</v>
       </c>
       <c r="F67" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="2:6">
@@ -3142,7 +3139,7 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="2:6">
@@ -3159,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="F69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="2:6">
@@ -3176,7 +3173,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -3193,7 +3190,7 @@
         <v>18</v>
       </c>
       <c r="F71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="2:6">
@@ -3210,7 +3207,7 @@
         <v>18</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="2:6">
@@ -3221,13 +3218,13 @@
         <v>6001</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
-      </c>
-      <c r="E73" t="s">
-        <v>18</v>
+        <v>78</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="2:6">
@@ -3238,13 +3235,13 @@
         <v>6001</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="2:6">
@@ -3255,13 +3252,13 @@
         <v>6001</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="2:6">
@@ -3272,13 +3269,13 @@
         <v>6001</v>
       </c>
       <c r="D76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="2:6">
@@ -3295,7 +3292,7 @@
         <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="2:6">
@@ -3312,7 +3309,7 @@
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="2:6">
@@ -3329,7 +3326,7 @@
         <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="2:6">
@@ -3346,7 +3343,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="81" spans="2:6">
@@ -3363,7 +3360,7 @@
         <v>18</v>
       </c>
       <c r="F81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="2:6">
@@ -3380,7 +3377,7 @@
         <v>18</v>
       </c>
       <c r="F82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="2:6">
@@ -3397,7 +3394,7 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="2:6">
@@ -3414,7 +3411,7 @@
         <v>18</v>
       </c>
       <c r="F84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="2:6">
@@ -3431,7 +3428,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="86" spans="2:6">
@@ -3442,13 +3439,13 @@
         <v>7001</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="2:6">
@@ -3459,13 +3456,13 @@
         <v>7001</v>
       </c>
       <c r="D87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="2:6">
@@ -3482,7 +3479,7 @@
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="2:6">
@@ -3499,7 +3496,7 @@
         <v>18</v>
       </c>
       <c r="F89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="2:6">
@@ -3516,7 +3513,7 @@
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="3:3">

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="23120" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -103,10 +103,10 @@
     <t>主城拼命想要掩盖的罪恶与冲突，在这片荒原上却一览无余。没记错的话，当年是反动派的手笔，才酿成了这里的悲剧？</t>
   </si>
   <si>
-    <t>怎么露出这种神情......“反动派”和那些拥护主城政府的“乐天派”之间的烂账，你不是早就心知肚明吗？</t>
-  </si>
-  <si>
-    <t>......你不正是为此而来吗？</t>
+    <t>怎么露出这种神情......&lt;b&gt;“反动派”&lt;/b&gt;和那些拥护主城政府的&lt;b&gt;“乐天派”&lt;/b&gt;之间的烂账，你不是早就心知肚明吗？</t>
+  </si>
+  <si>
+    <t>......你，不正是为此而来吗？</t>
   </si>
   <si>
     <t>清理&lt;b&gt;【蚀源虫】&lt;/b&gt;，收集净化污染的新型复合能量，主动申请加入&lt;b&gt;【荒原复苏计划】&lt;/b&gt;……你呀，总把自己当救世主。</t>
@@ -124,7 +124,7 @@
     <t>按 &lt;b&gt;&lt;color=#FF0000&gt;Shift键&lt;/color&gt;&lt;/b&gt; 或 &lt;b&gt;&lt;color=#FF0000&gt;space键&lt;/color&gt;&lt;/b&gt; 可进行冲刺。</t>
   </si>
   <si>
-    <t>影响比对完成。</t>
+    <t>影像比对完成。</t>
   </si>
   <si>
     <t>左侧是&lt;b&gt;【能量溶剂提取器】&lt;/b&gt;，可以提取属性为水的元素材料&lt;b&gt;&lt;color=#FF0000&gt;【能量溶剂】&lt;/color&gt;&lt;/b&gt;。</t>
@@ -173,7 +173,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>鼠标左键</t>
+      <t>鼠标&lt;b&gt;&lt;color=#FF0000&gt;左&lt;/color&gt;&lt;/b&gt;键</t>
     </r>
     <r>
       <rPr>
@@ -227,7 +227,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>鼠标右键</t>
+      <t>鼠标&lt;b&gt;&lt;color=#FF0000&gt;右&lt;/color&gt;&lt;/b&gt;键</t>
     </r>
     <r>
       <rPr>
@@ -374,7 +374,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>似乎能对这些虫子造成伤害，试试瞄准它们。</t>
+      <t>似乎能伤害这些虫子，试着瞄准它们。</t>
     </r>
   </si>
   <si>
@@ -687,24 +687,24 @@
     <t>随身终端</t>
   </si>
   <si>
-    <t>“随着&lt;b&gt;【荒原复苏计划】&lt;/b&gt;的全面铺开，多处废弃能量基地已相继完成重建。我们深信，在元素能量的引导下，那些曾罹患污染的人类领地，终将重回我们的怀抱…”</t>
-  </si>
-  <si>
-    <t>“曾经，我们的基地遭遇反动派的持续破坏，主城将汲取这样的教训，彻底——”</t>
-  </si>
-  <si>
-    <t>“当年是你们擅自提高了催化阀值！你们只需要能取之不尽的电池，是你们把脏水泼到——”</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“哔——”&lt;i&gt;&lt;color=#808080&gt;</t>
+    <t>“ 随着&lt;b&gt;【荒原复苏计划】&lt;/b&gt;的全面铺开，多处废弃能量基地已相继完成重建。我们深信，在元素能量的引导下，那些曾罹患污染的人类领地，终将重回我们的怀抱… ”</t>
+  </si>
+  <si>
+    <t>“ 曾经，我们的基地遭遇反动派的持续破坏，主城将汲取这样的教训，彻底—— ”</t>
+  </si>
+  <si>
+    <t>“ 当年是你们擅自提高了催化阀值！你们只需要取之不尽的电池，是你们把脏水泼到—— ”</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“ 哔—— ”&lt;i&gt;&lt;color=#808080&gt;</t>
     </r>
     <r>
       <rPr>
@@ -773,17 +773,10 @@
     </r>
   </si>
   <si>
-    <t>「【REC-006 基地元素反应催化记录】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+    <t>&lt;i&gt;「【REC-006 基地元素反应催化记录】&lt;/i&gt;</t>
+  </si>
+  <si>
+    <r>
       <t>  </t>
     </r>
     <r>
@@ -795,7 +788,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  __&lt;b&gt;</t>
+      <t xml:space="preserve">  __&lt;i&gt;&lt;b&gt;</t>
     </r>
     <r>
       <rPr>
@@ -818,7 +811,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>：上调27%(警告：已严重超过上限值）</t>
+      <t>：上调27%(警告：已严重超过上限值）&lt;/i&gt;</t>
     </r>
   </si>
   <si>
@@ -841,7 +834,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>__&lt;b&gt;</t>
+      <t>__&lt;i&gt;&lt;b&gt;</t>
     </r>
     <r>
       <rPr>
@@ -864,7 +857,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>：污染警报前</t>
+      <t>：污染警报前&lt;/i&gt;</t>
     </r>
   </si>
   <si>
@@ -887,7 +880,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> __&lt;b&gt;</t>
+      <t xml:space="preserve"> __&lt;i&gt;&lt;b&gt;</t>
     </r>
     <r>
       <rPr>
@@ -910,7 +903,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>：无法读取。」</t>
+      <t>：无法读取。」&lt;/i&gt;</t>
     </r>
   </si>
   <si>
@@ -932,7 +925,7 @@
     <t>备战吧，虫子可不会伤春悲秋。</t>
   </si>
   <si>
-    <t>元素能量的波动正在逐渐减小，或许你马上就可以喘口气了。</t>
+    <t>元素能量的波动在逐渐减小，或许你马上就可以喘口气了。</t>
   </si>
   <si>
     <t>在那之前，别掉以轻心。</t>
@@ -1141,7 +1134,6 @@
     </font>
     <font>
       <b/>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1158,6 +1150,7 @@
     </font>
     <font>
       <b/>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1959,11 +1952,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F118"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="7.96363636363636" customWidth="1"/>
-    <col min="3" max="3" width="11.8090909090909" customWidth="1"/>
-    <col min="4" max="4" width="15.9454545454545" customWidth="1"/>
+    <col min="2" max="2" width="7.96153846153846" customWidth="1"/>
+    <col min="3" max="3" width="11.8076923076923" customWidth="1"/>
+    <col min="4" max="4" width="15.9423076923077" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2244,7 +2237,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="1:6">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2346,7 +2339,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" ht="17" spans="2:6">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2363,7 +2356,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" ht="17" spans="2:6">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2397,7 +2390,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" ht="17" spans="2:6">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2431,7 +2424,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" ht="17" spans="2:6">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2601,7 +2594,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" ht="17" spans="2:6">
       <c r="B37" s="4">
         <v>33</v>
       </c>
@@ -2635,7 +2628,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" ht="17" spans="2:6">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -2805,7 +2798,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" ht="17" spans="2:6">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -2839,7 +2832,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" ht="17" spans="2:6">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -2924,7 +2917,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" ht="17" spans="2:6">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -3026,7 +3019,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" ht="17" spans="2:6">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -3196,7 +3189,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" ht="17" spans="2:6">
       <c r="B72" s="4">
         <v>68</v>
       </c>
@@ -3230,7 +3223,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" ht="17" spans="2:6">
       <c r="B74" s="4">
         <v>70</v>
       </c>
@@ -3247,7 +3240,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="2:6">
+    <row r="75" ht="17" spans="2:6">
       <c r="B75" s="4">
         <v>71</v>
       </c>
@@ -3264,7 +3257,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" ht="17" spans="2:6">
       <c r="B76" s="4">
         <v>72</v>
       </c>
@@ -3519,22 +3512,22 @@
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="3:3">
+    <row r="91" spans="2:6">
       <c r="C91" s="4"/>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="2:6">
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="2:6">
       <c r="C93" s="4"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="2:6">
       <c r="C94" s="4"/>
     </row>
-    <row r="95" spans="3:3">
+    <row r="95" spans="2:6">
       <c r="C95" s="4"/>
     </row>
-    <row r="96" spans="2:2">
+    <row r="96" spans="2:6">
       <c r="B96" s="4"/>
     </row>
     <row r="97" spans="2:2">
@@ -3585,19 +3578,19 @@
     <row r="112" spans="2:2">
       <c r="B112" s="4"/>
     </row>
-    <row r="113" spans="2:2">
+    <row r="113" spans="2:6">
       <c r="B113" s="4"/>
     </row>
-    <row r="114" spans="2:2">
+    <row r="114" spans="2:6">
       <c r="B114" s="4"/>
     </row>
-    <row r="115" spans="2:2">
+    <row r="115" spans="2:6">
       <c r="B115" s="4"/>
     </row>
-    <row r="116" spans="2:2">
+    <row r="116" spans="2:6">
       <c r="B116" s="4"/>
     </row>
-    <row r="117" spans="2:2">
+    <row r="117" spans="2:6">
       <c r="B117" s="4"/>
     </row>
     <row r="118" spans="2:6">
@@ -3615,7 +3608,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3627,7 +3620,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23120" windowHeight="13660"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="109">
   <si>
     <t>##var</t>
   </si>
@@ -275,9 +275,6 @@
     <t>催化发射器运行正常，开了个好头。</t>
   </si>
   <si>
-    <t>主题bgm</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -777,6 +774,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>  </t>
     </r>
     <r>
@@ -1135,7 +1139,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFD83931"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1143,7 +1147,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFD83931"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1952,11 +1956,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F118"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="7.96153846153846" customWidth="1"/>
-    <col min="3" max="3" width="11.8076923076923" customWidth="1"/>
-    <col min="4" max="4" width="15.9423076923077" customWidth="1"/>
+    <col min="2" max="2" width="7.96363636363636" customWidth="1"/>
+    <col min="3" max="3" width="11.8090909090909" customWidth="1"/>
+    <col min="4" max="4" width="15.9454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2237,7 +2241,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="2:6">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2339,7 +2343,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="2:6">
+    <row r="22" spans="2:6">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2356,7 +2360,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="2:6">
+    <row r="23" spans="2:6">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2390,7 +2394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" ht="17" spans="2:6">
+    <row r="25" spans="2:6">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2401,10 +2405,10 @@
         <v>20</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -2421,10 +2425,10 @@
         <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" ht="17" spans="2:6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2438,7 +2442,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="2:6">
@@ -2451,11 +2455,11 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" t="s">
-        <v>18</v>
+      <c r="E28" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -2472,7 +2476,7 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -2489,7 +2493,7 @@
         <v>18</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -2506,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -2523,7 +2527,7 @@
         <v>18</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="2:6">
@@ -2540,7 +2544,7 @@
         <v>18</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="2:6">
@@ -2557,7 +2561,7 @@
         <v>18</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -2570,11 +2574,11 @@
       <c r="D35" t="s">
         <v>20</v>
       </c>
-      <c r="E35" t="s">
-        <v>18</v>
+      <c r="E35" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -2591,10 +2595,10 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" ht="17" spans="2:6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="4">
         <v>33</v>
       </c>
@@ -2608,7 +2612,7 @@
         <v>18</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -2625,10 +2629,10 @@
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" ht="17" spans="2:6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -2642,7 +2646,7 @@
         <v>18</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -2655,11 +2659,11 @@
       <c r="D40" t="s">
         <v>20</v>
       </c>
-      <c r="E40" t="s">
-        <v>18</v>
+      <c r="E40" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="2:6">
@@ -2676,7 +2680,7 @@
         <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="2:6">
@@ -2693,7 +2697,7 @@
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -2710,7 +2714,7 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="2:6">
@@ -2727,7 +2731,7 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="2:6">
@@ -2744,7 +2748,7 @@
         <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="2:6">
@@ -2761,7 +2765,7 @@
         <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -2778,7 +2782,7 @@
         <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -2795,10 +2799,10 @@
         <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" ht="17" spans="2:6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -2812,7 +2816,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="2:6">
@@ -2829,10 +2833,10 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" ht="17" spans="2:6">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -2846,7 +2850,7 @@
         <v>18</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="2:6">
@@ -2863,7 +2867,7 @@
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="2:6">
@@ -2880,7 +2884,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="2:6">
@@ -2897,7 +2901,7 @@
         <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="2:6">
@@ -2914,10 +2918,10 @@
         <v>18</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="56" ht="17" spans="2:6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -2931,7 +2935,7 @@
         <v>18</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="2:6">
@@ -2948,7 +2952,7 @@
         <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="2:6">
@@ -2965,7 +2969,7 @@
         <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2976,13 +2980,13 @@
         <v>5001</v>
       </c>
       <c r="D59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
         <v>79</v>
-      </c>
-      <c r="E59" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="60" spans="2:6">
@@ -2993,13 +2997,13 @@
         <v>5001</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -3010,16 +3014,16 @@
         <v>5001</v>
       </c>
       <c r="D61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62" ht="17" spans="2:6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -3027,13 +3031,13 @@
         <v>5001</v>
       </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="2:6">
@@ -3050,7 +3054,7 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -3067,7 +3071,7 @@
         <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -3084,7 +3088,7 @@
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -3101,7 +3105,7 @@
         <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="2:6">
@@ -3118,7 +3122,7 @@
         <v>18</v>
       </c>
       <c r="F67" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="2:6">
@@ -3135,7 +3139,7 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="2:6">
@@ -3152,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="F69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="2:6">
@@ -3169,7 +3173,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -3186,10 +3190,10 @@
         <v>18</v>
       </c>
       <c r="F71" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" ht="17" spans="2:6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
       <c r="B72" s="4">
         <v>68</v>
       </c>
@@ -3203,7 +3207,7 @@
         <v>18</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="2:6">
@@ -3214,16 +3218,16 @@
         <v>6001</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
-      </c>
-      <c r="E73" t="s">
-        <v>18</v>
+        <v>78</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" ht="17" spans="2:6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6">
       <c r="B74" s="4">
         <v>70</v>
       </c>
@@ -3231,16 +3235,16 @@
         <v>6001</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="75" ht="17" spans="2:6">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
       <c r="B75" s="4">
         <v>71</v>
       </c>
@@ -3248,16 +3252,16 @@
         <v>6001</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" ht="17" spans="2:6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="4">
         <v>72</v>
       </c>
@@ -3265,13 +3269,13 @@
         <v>6001</v>
       </c>
       <c r="D76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="2:6">
@@ -3288,7 +3292,7 @@
         <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="2:6">
@@ -3305,7 +3309,7 @@
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="2:6">
@@ -3322,7 +3326,7 @@
         <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="2:6">
@@ -3339,7 +3343,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="81" spans="2:6">
@@ -3356,7 +3360,7 @@
         <v>18</v>
       </c>
       <c r="F81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="2:6">
@@ -3373,7 +3377,7 @@
         <v>18</v>
       </c>
       <c r="F82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="2:6">
@@ -3390,7 +3394,7 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="2:6">
@@ -3407,7 +3411,7 @@
         <v>18</v>
       </c>
       <c r="F84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="2:6">
@@ -3424,7 +3428,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="86" spans="2:6">
@@ -3435,13 +3439,13 @@
         <v>7001</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="2:6">
@@ -3452,13 +3456,13 @@
         <v>7001</v>
       </c>
       <c r="D87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="2:6">
@@ -3475,7 +3479,7 @@
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="2:6">
@@ -3492,7 +3496,7 @@
         <v>18</v>
       </c>
       <c r="F89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="2:6">
@@ -3509,25 +3513,25 @@
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="91" spans="2:6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3">
       <c r="C91" s="4"/>
     </row>
-    <row r="92" spans="2:6">
+    <row r="92" spans="3:3">
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="2:6">
+    <row r="93" spans="3:3">
       <c r="C93" s="4"/>
     </row>
-    <row r="94" spans="2:6">
+    <row r="94" spans="3:3">
       <c r="C94" s="4"/>
     </row>
-    <row r="95" spans="2:6">
+    <row r="95" spans="3:3">
       <c r="C95" s="4"/>
     </row>
-    <row r="96" spans="2:6">
+    <row r="96" spans="2:2">
       <c r="B96" s="4"/>
     </row>
     <row r="97" spans="2:2">
@@ -3578,19 +3582,19 @@
     <row r="112" spans="2:2">
       <c r="B112" s="4"/>
     </row>
-    <row r="113" spans="2:6">
+    <row r="113" spans="2:2">
       <c r="B113" s="4"/>
     </row>
-    <row r="114" spans="2:6">
+    <row r="114" spans="2:2">
       <c r="B114" s="4"/>
     </row>
-    <row r="115" spans="2:6">
+    <row r="115" spans="2:2">
       <c r="B115" s="4"/>
     </row>
-    <row r="116" spans="2:6">
+    <row r="116" spans="2:2">
       <c r="B116" s="4"/>
     </row>
-    <row r="117" spans="2:6">
+    <row r="117" spans="2:2">
       <c r="B117" s="4"/>
     </row>
     <row r="118" spans="2:6">
@@ -3608,7 +3612,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3620,7 +3624,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>催化发射器运行正常，开了个好头。</t>
+  </si>
+  <si>
+    <t>主题bgm</t>
   </si>
   <si>
     <r>
@@ -1139,7 +1142,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFD83931"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1147,7 +1150,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFD83931"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF8F959E"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1157,14 +1168,6 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF8F959E"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2405,10 +2408,10 @@
         <v>20</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -2425,7 +2428,7 @@
         <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -2442,7 +2445,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:6">
@@ -2459,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -2476,7 +2479,7 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -2493,7 +2496,7 @@
         <v>18</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -2510,7 +2513,7 @@
         <v>18</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -2527,7 +2530,7 @@
         <v>18</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="2:6">
@@ -2544,7 +2547,7 @@
         <v>18</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="2:6">
@@ -2561,7 +2564,7 @@
         <v>18</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -2578,7 +2581,7 @@
         <v>21</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -2595,7 +2598,7 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="2:6">
@@ -2612,7 +2615,7 @@
         <v>18</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -2629,7 +2632,7 @@
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="2:6">
@@ -2646,7 +2649,7 @@
         <v>18</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -2663,7 +2666,7 @@
         <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="2:6">
@@ -2680,7 +2683,7 @@
         <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="2:6">
@@ -2697,7 +2700,7 @@
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -2714,7 +2717,7 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="2:6">
@@ -2731,7 +2734,7 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="2:6">
@@ -2748,7 +2751,7 @@
         <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="2:6">
@@ -2765,7 +2768,7 @@
         <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -2782,7 +2785,7 @@
         <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -2799,7 +2802,7 @@
         <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -2816,7 +2819,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="2:6">
@@ -2833,7 +2836,7 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -2850,7 +2853,7 @@
         <v>18</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="2:6">
@@ -2867,7 +2870,7 @@
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="2:6">
@@ -2884,7 +2887,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="2:6">
@@ -2901,7 +2904,7 @@
         <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="2:6">
@@ -2918,7 +2921,7 @@
         <v>18</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="2:6">
@@ -2935,7 +2938,7 @@
         <v>18</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="2:6">
@@ -2952,7 +2955,7 @@
         <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="2:6">
@@ -2969,7 +2972,7 @@
         <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2980,13 +2983,13 @@
         <v>5001</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F59" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="2:6">
@@ -2997,13 +3000,13 @@
         <v>5001</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -3014,13 +3017,13 @@
         <v>5001</v>
       </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -3031,13 +3034,13 @@
         <v>5001</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="2:6">
@@ -3054,7 +3057,7 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -3071,7 +3074,7 @@
         <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -3088,7 +3091,7 @@
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -3105,7 +3108,7 @@
         <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="2:6">
@@ -3122,7 +3125,7 @@
         <v>18</v>
       </c>
       <c r="F67" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="2:6">
@@ -3139,7 +3142,7 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="2:6">
@@ -3156,7 +3159,7 @@
         <v>18</v>
       </c>
       <c r="F69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="2:6">
@@ -3173,7 +3176,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -3190,7 +3193,7 @@
         <v>18</v>
       </c>
       <c r="F71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="2:6">
@@ -3207,7 +3210,7 @@
         <v>18</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="2:6">
@@ -3218,13 +3221,13 @@
         <v>6001</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="2:6">
@@ -3235,13 +3238,13 @@
         <v>6001</v>
       </c>
       <c r="D74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="2:6">
@@ -3252,13 +3255,13 @@
         <v>6001</v>
       </c>
       <c r="D75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="2:6">
@@ -3269,13 +3272,13 @@
         <v>6001</v>
       </c>
       <c r="D76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="2:6">
@@ -3292,7 +3295,7 @@
         <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="2:6">
@@ -3309,7 +3312,7 @@
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="2:6">
@@ -3326,7 +3329,7 @@
         <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="2:6">
@@ -3343,7 +3346,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="2:6">
@@ -3360,7 +3363,7 @@
         <v>18</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="2:6">
@@ -3377,7 +3380,7 @@
         <v>18</v>
       </c>
       <c r="F82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="2:6">
@@ -3394,7 +3397,7 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="2:6">
@@ -3411,7 +3414,7 @@
         <v>18</v>
       </c>
       <c r="F84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="2:6">
@@ -3428,7 +3431,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="2:6">
@@ -3439,13 +3442,13 @@
         <v>7001</v>
       </c>
       <c r="D86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F86" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="87" spans="2:6">
@@ -3456,13 +3459,13 @@
         <v>7001</v>
       </c>
       <c r="D87" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="2:6">
@@ -3479,7 +3482,7 @@
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="2:6">
@@ -3496,7 +3499,7 @@
         <v>18</v>
       </c>
       <c r="F89" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="2:6">
@@ -3513,7 +3516,7 @@
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="3:3">

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>催化发射器运行正常，开了个好头。</t>
+  </si>
+  <si>
+    <t>主题bgm</t>
   </si>
   <si>
     <r>
@@ -1139,7 +1142,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFD83931"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1147,7 +1150,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFD83931"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2405,10 +2408,10 @@
         <v>20</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="2:6">
@@ -2425,7 +2428,7 @@
         <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -2442,7 +2445,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:6">
@@ -2459,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -2476,7 +2479,7 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -2493,7 +2496,7 @@
         <v>18</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -2510,7 +2513,7 @@
         <v>18</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -2527,7 +2530,7 @@
         <v>18</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="2:6">
@@ -2544,7 +2547,7 @@
         <v>18</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="2:6">
@@ -2561,7 +2564,7 @@
         <v>18</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="2:6">
@@ -2578,7 +2581,7 @@
         <v>21</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="2:6">
@@ -2595,7 +2598,7 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="2:6">
@@ -2612,7 +2615,7 @@
         <v>18</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -2629,7 +2632,7 @@
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="2:6">
@@ -2646,7 +2649,7 @@
         <v>18</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -2663,7 +2666,7 @@
         <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="2:6">
@@ -2680,7 +2683,7 @@
         <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="2:6">
@@ -2697,7 +2700,7 @@
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -2714,7 +2717,7 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="2:6">
@@ -2731,7 +2734,7 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="2:6">
@@ -2748,7 +2751,7 @@
         <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="2:6">
@@ -2765,7 +2768,7 @@
         <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="2:6">
@@ -2782,7 +2785,7 @@
         <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="2:6">
@@ -2799,7 +2802,7 @@
         <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -2816,7 +2819,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="2:6">
@@ -2833,7 +2836,7 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -2850,7 +2853,7 @@
         <v>18</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="2:6">
@@ -2867,7 +2870,7 @@
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="2:6">
@@ -2884,7 +2887,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="2:6">
@@ -2901,7 +2904,7 @@
         <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="2:6">
@@ -2918,7 +2921,7 @@
         <v>18</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="2:6">
@@ -2935,7 +2938,7 @@
         <v>18</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="2:6">
@@ -2952,7 +2955,7 @@
         <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="2:6">
@@ -2969,7 +2972,7 @@
         <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2980,13 +2983,13 @@
         <v>5001</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F59" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="2:6">
@@ -2997,13 +3000,13 @@
         <v>5001</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -3014,13 +3017,13 @@
         <v>5001</v>
       </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -3031,13 +3034,13 @@
         <v>5001</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="2:6">
@@ -3054,7 +3057,7 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -3071,7 +3074,7 @@
         <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -3088,7 +3091,7 @@
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -3105,7 +3108,7 @@
         <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="2:6">
@@ -3122,7 +3125,7 @@
         <v>18</v>
       </c>
       <c r="F67" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="2:6">
@@ -3139,7 +3142,7 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="2:6">
@@ -3156,7 +3159,7 @@
         <v>18</v>
       </c>
       <c r="F69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="2:6">
@@ -3173,7 +3176,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -3190,7 +3193,7 @@
         <v>18</v>
       </c>
       <c r="F71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="2:6">
@@ -3207,7 +3210,7 @@
         <v>18</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="2:6">
@@ -3218,13 +3221,13 @@
         <v>6001</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="2:6">
@@ -3235,13 +3238,13 @@
         <v>6001</v>
       </c>
       <c r="D74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="2:6">
@@ -3252,13 +3255,13 @@
         <v>6001</v>
       </c>
       <c r="D75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="2:6">
@@ -3269,13 +3272,13 @@
         <v>6001</v>
       </c>
       <c r="D76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="2:6">
@@ -3292,7 +3295,7 @@
         <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="2:6">
@@ -3309,7 +3312,7 @@
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="2:6">
@@ -3326,7 +3329,7 @@
         <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="2:6">
@@ -3343,7 +3346,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="2:6">
@@ -3360,7 +3363,7 @@
         <v>18</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="2:6">
@@ -3377,7 +3380,7 @@
         <v>18</v>
       </c>
       <c r="F82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="2:6">
@@ -3394,7 +3397,7 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="2:6">
@@ -3411,7 +3414,7 @@
         <v>18</v>
       </c>
       <c r="F84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="2:6">
@@ -3428,7 +3431,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="2:6">
@@ -3439,13 +3442,13 @@
         <v>7001</v>
       </c>
       <c r="D86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F86" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="87" spans="2:6">
@@ -3456,13 +3459,13 @@
         <v>7001</v>
       </c>
       <c r="D87" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="2:6">
@@ -3479,7 +3482,7 @@
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="2:6">
@@ -3496,7 +3499,7 @@
         <v>18</v>
       </c>
       <c r="F89" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="2:6">
@@ -3513,7 +3516,7 @@
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="3:3">

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="23120" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,10 +127,10 @@
     <t>影像比对完成。</t>
   </si>
   <si>
-    <t>左侧是&lt;b&gt;【能量溶剂提取器】&lt;/b&gt;，可以提取属性为水的元素材料&lt;b&gt;&lt;color=#FF0000&gt;【能量溶剂】&lt;/color&gt;&lt;/b&gt;。</t>
-  </si>
-  <si>
-    <t>前方是&lt;b&gt;【荒原基质提取器】&lt;/b&gt;，可以提取属性为土的元素材料&lt;b&gt;&lt;color=#FF0000&gt;【荒原基质】&lt;/color&gt;&lt;/b&gt;。</t>
+    <t>&lt;b&gt;【能量溶剂提取器】&lt;/b&gt;，可以提取属性为水的元素材料&lt;b&gt;&lt;color=#FF0000&gt;【能量溶剂】&lt;/color&gt;&lt;/b&gt;。</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;【荒原基质提取器】&lt;/b&gt;，可以提取属性为土的元素材料&lt;b&gt;&lt;color=#FF0000&gt;【荒原基质】&lt;/color&gt;&lt;/b&gt;。</t>
   </si>
   <si>
     <t>这边还有一座修复生命体征的&lt;b&gt;&lt;color=#FF0000&gt;【活性重构仪】&lt;/color&gt;&lt;/b&gt;。设备完好率达 82%......还挺幸运。</t>
@@ -1142,14 +1142,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFD83931"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1157,7 +1149,6 @@
     </font>
     <font>
       <b/>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1168,6 +1159,15 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF8F959E"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1959,11 +1959,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F118"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="7.96363636363636" customWidth="1"/>
-    <col min="3" max="3" width="11.8090909090909" customWidth="1"/>
-    <col min="4" max="4" width="15.9454545454545" customWidth="1"/>
+    <col min="2" max="2" width="7.96153846153846" customWidth="1"/>
+    <col min="3" max="3" width="11.8076923076923" customWidth="1"/>
+    <col min="4" max="4" width="15.9423076923077" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2244,7 +2244,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="1:6">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" ht="17" spans="2:6">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" ht="17" spans="2:6">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" ht="17" spans="2:6">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" ht="17" spans="2:6">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
         <v>48</v>
@@ -2578,7 +2578,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
         <v>55</v>
@@ -2601,7 +2601,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" ht="17" spans="2:6">
       <c r="B37" s="4">
         <v>33</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" ht="17" spans="2:6">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
         <v>60</v>
@@ -2805,7 +2805,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" ht="17" spans="2:6">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" ht="17" spans="2:6">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" ht="17" spans="2:6">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" ht="17" spans="2:6">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -3155,8 +3155,8 @@
       <c r="D69" t="s">
         <v>38</v>
       </c>
-      <c r="E69" t="s">
-        <v>18</v>
+      <c r="E69" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="F69" t="s">
         <v>67</v>
@@ -3196,7 +3196,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" ht="17" spans="2:6">
       <c r="B72" s="4">
         <v>68</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" ht="17" spans="2:6">
       <c r="B74" s="4">
         <v>70</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="2:6">
+    <row r="75" ht="17" spans="2:6">
       <c r="B75" s="4">
         <v>71</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" ht="17" spans="2:6">
       <c r="B76" s="4">
         <v>72</v>
       </c>
@@ -3376,8 +3376,8 @@
       <c r="D82" t="s">
         <v>38</v>
       </c>
-      <c r="E82" t="s">
-        <v>18</v>
+      <c r="E82" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="F82" t="s">
         <v>101</v>
@@ -3519,22 +3519,22 @@
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="3:3">
+    <row r="91" spans="2:6">
       <c r="C91" s="4"/>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="2:6">
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="2:6">
       <c r="C93" s="4"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="2:6">
       <c r="C94" s="4"/>
     </row>
-    <row r="95" spans="3:3">
+    <row r="95" spans="2:6">
       <c r="C95" s="4"/>
     </row>
-    <row r="96" spans="2:2">
+    <row r="96" spans="2:6">
       <c r="B96" s="4"/>
     </row>
     <row r="97" spans="2:2">
@@ -3585,19 +3585,19 @@
     <row r="112" spans="2:2">
       <c r="B112" s="4"/>
     </row>
-    <row r="113" spans="2:2">
+    <row r="113" spans="2:6">
       <c r="B113" s="4"/>
     </row>
-    <row r="114" spans="2:2">
+    <row r="114" spans="2:6">
       <c r="B114" s="4"/>
     </row>
-    <row r="115" spans="2:2">
+    <row r="115" spans="2:6">
       <c r="B115" s="4"/>
     </row>
-    <row r="116" spans="2:2">
+    <row r="116" spans="2:6">
       <c r="B116" s="4"/>
     </row>
-    <row r="117" spans="2:2">
+    <row r="117" spans="2:6">
       <c r="B117" s="4"/>
     </row>
     <row r="118" spans="2:6">
@@ -3615,7 +3615,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3627,7 +3627,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -106,7 +106,7 @@
     <t>怎么露出这种神情......&lt;b&gt;“反动派”&lt;/b&gt;和那些拥护主城政府的&lt;b&gt;“乐天派”&lt;/b&gt;之间的烂账，你不是早就心知肚明吗？</t>
   </si>
   <si>
-    <t>......你，不正是为此而来吗？</t>
+    <t>……你，不正是为此而来吗？</t>
   </si>
   <si>
     <t>清理&lt;b&gt;【蚀源虫】&lt;/b&gt;，收集净化污染的新型复合能量，主动申请加入&lt;b&gt;【荒原复苏计划】&lt;/b&gt;……你呀，总把自己当救世主。</t>
@@ -719,7 +719,7 @@
     </r>
   </si>
   <si>
-    <t>......</t>
+    <t>……</t>
   </si>
   <si>
     <t>在杀虫之余，居然还有闲心听上这么一段惬意的新闻广播。</t>
@@ -941,16 +941,16 @@
     <t>快要日落了，这会是最后一波吗？</t>
   </si>
   <si>
-    <t>“我们曾满怀伤痛，曾历经狂热，我们也曾坚信元素能抚平一切……在那些繁荣与宏大背后，有多少被掩埋的真相与代价......”</t>
+    <t>“我们曾满怀伤痛，曾历经狂热，我们也曾坚信元素能抚平一切……在那些繁荣与宏大背后，有多少被掩埋的真相与代价……”</t>
   </si>
   <si>
     <t>“尽管如此，无论是顺从的盲目，还是清醒的抗争，我们依然渴望——去触碰那个真正不再满目疮痍的世界……”</t>
   </si>
   <si>
-    <t>终于要结束了——惊心动魄的一天。</t>
-  </si>
-  <si>
-    <t>......你在看什么？</t>
+    <t>能量波动趋于平稳——呼……终于结束了。</t>
+  </si>
+  <si>
+    <t>……你在看什么？</t>
   </si>
   <si>
     <t>啊......</t>
@@ -1142,23 +1142,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFD83931"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF8F959E"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1168,6 +1152,22 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFD83931"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF8F959E"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -479,7 +479,7 @@
     </r>
   </si>
   <si>
-    <t>地形可不分敌我，你自己也小心。</t>
+    <t>注意安全。</t>
   </si>
   <si>
     <r>
@@ -1141,14 +1141,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1168,6 +1160,14 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF8F959E"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -106,7 +106,7 @@
     <t>怎么露出这种神情......&lt;b&gt;“反动派”&lt;/b&gt;和那些拥护主城政府的&lt;b&gt;“乐天派”&lt;/b&gt;之间的烂账，你不是早就心知肚明吗？</t>
   </si>
   <si>
-    <t>......你，不正是为此而来吗？</t>
+    <t>……你，不正是为此而来吗？</t>
   </si>
   <si>
     <t>清理&lt;b&gt;【蚀源虫】&lt;/b&gt;，收集净化污染的新型复合能量，主动申请加入&lt;b&gt;【荒原复苏计划】&lt;/b&gt;……你呀，总把自己当救世主。</t>
@@ -479,7 +479,7 @@
     </r>
   </si>
   <si>
-    <t>地形可不分敌我，你自己也小心。</t>
+    <t>注意安全。</t>
   </si>
   <si>
     <r>
@@ -719,7 +719,7 @@
     </r>
   </si>
   <si>
-    <t>......</t>
+    <t>……</t>
   </si>
   <si>
     <t>在杀虫之余，居然还有闲心听上这么一段惬意的新闻广播。</t>
@@ -941,16 +941,16 @@
     <t>快要日落了，这会是最后一波吗？</t>
   </si>
   <si>
-    <t>“我们曾满怀伤痛，曾历经狂热，我们也曾坚信元素能抚平一切……在那些繁荣与宏大背后，有多少被掩埋的真相与代价......”</t>
+    <t>“我们曾满怀伤痛，曾历经狂热，我们也曾坚信元素能抚平一切……在那些繁荣与宏大背后，有多少被掩埋的真相与代价……”</t>
   </si>
   <si>
     <t>“尽管如此，无论是顺从的盲目，还是清醒的抗争，我们依然渴望——去触碰那个真正不再满目疮痍的世界……”</t>
   </si>
   <si>
-    <t>终于要结束了——惊心动魄的一天。</t>
-  </si>
-  <si>
-    <t>......你在看什么？</t>
+    <t>能量波动趋于平稳——呼……终于结束了。</t>
+  </si>
+  <si>
+    <t>……你在看什么？</t>
   </si>
   <si>
     <t>啊......</t>
@@ -1141,8 +1141,9 @@
     </font>
     <font>
       <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFD83931"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1150,7 +1151,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFD83931"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1165,7 +1166,6 @@
     </font>
     <font>
       <b/>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>

--- a/ConfigWorkspace/Data/slot_dialogue.xlsx
+++ b/ConfigWorkspace/Data/slot_dialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -515,7 +515,42 @@
     </r>
   </si>
   <si>
-    <t>趁你战斗的时候，我分析了一下基地的残留数据。</t>
+    <t>那些怪物身上掉落的晶体似乎自动吸附到你的储物器里了——啊，是&lt;b&gt;&lt;color=#FF0000&gt;【原素结晶】&lt;/color&gt;&lt;/b&gt;。</t>
+  </si>
+  <si>
+    <r>
+      <t>真是幸运啊，这不就是你想要的新型复合能量载体吗？但你的储物器真得升升级了，&lt;b&gt;&lt;color=#FF0000&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFD83931"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【原素结晶】&lt;/color&gt;&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的储备上限居然只有&lt;b&gt;&lt;color=#FF0000&gt;【3】&lt;/color&gt;&lt;/b&gt;。</t>
+    </r>
+  </si>
+  <si>
+    <t>拿它来净化污染......真讽刺啊，毁灭这里的，是暴虐失控的元素；但能抚平这道伤疤的，居然也是它。</t>
+  </si>
+  <si>
+    <t>待会儿在这片荒原的地块上试试看，但小心点，这东西的性质可不太稳定，不同的颜色应该对应着不同的属性效果。</t>
+  </si>
+  <si>
+    <t>不说那些了，趁你战斗的时候，我分析了一下基地的残留数据。</t>
   </si>
   <si>
     <t>你猜怎么着，REC-006 的所有核心资料库，居然都被故意执行了毁沉指令。</t>
@@ -542,20 +577,44 @@
     <t>总之，保护好自己。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>你从那些虫子身上捡了什么东西回来？——啊，是&lt;b&gt;&lt;color=#FF0000&gt;</t>
+    <t>按 &lt;b&gt;&lt;color=#FF0000&gt;E 键&lt;/color&gt;&lt;/b&gt; 消耗&lt;b&gt;&lt;color=#FF0000&gt;【原素结晶】&lt;/color&gt;&lt;/b&gt;，可生成【特殊地形】。按 &lt;b&gt;&lt;color=#FF0000&gt;Q键&lt;/color&gt;&lt;/b&gt; 可丢弃 / 拾取。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>击败&lt;b&gt;</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【精英·蚀源虫】&lt;/b&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>有几率掉落&lt;b&gt;&lt;color=#FF0000&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <color rgb="FFD83931"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -565,6 +624,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
@@ -575,109 +635,6 @@
     </r>
   </si>
   <si>
-    <t>恭喜你，终于找到了想要的新型复合能量载体。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>但你的储物器真得升升级了，&lt;b&gt;&lt;color=#FF0000&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFD83931"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【原素结晶】&lt;/color&gt;&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的储备上限居然只有&lt;b&gt;&lt;color=#FF0000&gt;【3】&lt;/color&gt;&lt;/b&gt;。</t>
-    </r>
-  </si>
-  <si>
-    <t>嗯......虽然它还不是完全体，但强制改写环境的能力，也绰绰有余了。</t>
-  </si>
-  <si>
-    <t>拿它来净化污染......呵，毁灭这里的，是暴虐失控的元素；但能抚平这道伤疤的，居然也是它。</t>
-  </si>
-  <si>
-    <t>小心使用。这东西的性质可不太稳定。</t>
-  </si>
-  <si>
-    <t>按 &lt;b&gt;&lt;color=#FF0000&gt;E 键&lt;/color&gt;&lt;/b&gt; 消耗&lt;b&gt;&lt;color=#FF0000&gt;【原素结晶】&lt;/color&gt;&lt;/b&gt;，可生成【特殊地形】，按 &lt;b&gt;&lt;color=#FF0000&gt;Q键&lt;/color&gt;&lt;/b&gt; 可丢弃 / 拾取。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>击败&lt;b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【精英·蚀源虫】&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>有几率掉落&lt;b&gt;&lt;color=#FF0000&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFD83931"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【原素结晶】&lt;/color&gt;&lt;/b&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
     <t>检测仪器感应到【蚀源虫】正在靠近。</t>
   </si>
   <si>
@@ -735,6 +692,12 @@
   </si>
   <si>
     <t>虽说没办法破解云端数据，但基地提取器里还残留着一部分运行缓存，我正在想办法破解，你别担心。</t>
+  </si>
+  <si>
+    <t>我相信你的杀虫能力，你也相信我的破译技术。</t>
+  </si>
+  <si>
+    <t>保护好自己。</t>
   </si>
   <si>
     <t>【蚀源虫】怎么越来越多了。</t>
@@ -1151,7 +1114,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFD83931"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1167,7 +1130,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFD83931"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1958,7 +1921,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="7.96153846153846" customWidth="1"/>
@@ -2662,14 +2625,14 @@
       <c r="D40" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" ht="17" spans="2:6">
       <c r="B41" s="4">
         <v>37</v>
       </c>
@@ -2682,7 +2645,7 @@
       <c r="E41" t="s">
         <v>18</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2713,7 +2676,7 @@
       <c r="D43" t="s">
         <v>20</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F43" t="s">
@@ -2730,7 +2693,7 @@
       <c r="D44" t="s">
         <v>20</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F44" t="s">
@@ -2779,7 +2742,7 @@
         <v>4001</v>
       </c>
       <c r="D47" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
         <v>18</v>
@@ -2796,7 +2759,7 @@
         <v>4001</v>
       </c>
       <c r="D48" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
         <v>18</v>
@@ -2805,12 +2768,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" ht="17" spans="2:6">
+    <row r="49" spans="2:6">
       <c r="B49" s="4">
         <v>45</v>
       </c>
       <c r="C49">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D49" t="s">
         <v>20</v>
@@ -2818,7 +2781,7 @@
       <c r="E49" t="s">
         <v>18</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2827,7 +2790,7 @@
         <v>46</v>
       </c>
       <c r="C50">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D50" t="s">
         <v>20</v>
@@ -2839,20 +2802,20 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" ht="17" spans="2:6">
+    <row r="51" spans="2:6">
       <c r="B51" s="4">
         <v>47</v>
       </c>
       <c r="C51">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D51" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E51" t="s">
         <v>18</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2861,10 +2824,10 @@
         <v>48</v>
       </c>
       <c r="C52">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E52" t="s">
         <v>18</v>
@@ -2878,32 +2841,32 @@
         <v>49</v>
       </c>
       <c r="C53">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E53" t="s">
         <v>18</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" ht="17" spans="2:6">
       <c r="B54" s="4">
         <v>50</v>
       </c>
       <c r="C54">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E54" t="s">
         <v>18</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2915,16 +2878,16 @@
         <v>4002</v>
       </c>
       <c r="D55" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E55" t="s">
         <v>18</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="56" ht="17" spans="2:6">
+    <row r="56" spans="2:6">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -2932,12 +2895,12 @@
         <v>4002</v>
       </c>
       <c r="D56" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E56" t="s">
         <v>18</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2946,16 +2909,16 @@
         <v>53</v>
       </c>
       <c r="C57">
-        <v>4002</v>
+        <v>5001</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
-      </c>
-      <c r="E57" t="s">
-        <v>18</v>
+        <v>77</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="2:6">
@@ -2963,16 +2926,16 @@
         <v>54</v>
       </c>
       <c r="C58">
-        <v>4002</v>
+        <v>5001</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="E58" t="s">
         <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2983,16 +2946,16 @@
         <v>5001</v>
       </c>
       <c r="D59" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
       </c>
       <c r="F59" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" ht="17" spans="2:6">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -3000,12 +2963,12 @@
         <v>5001</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E60" t="s">
         <v>18</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3017,7 +2980,7 @@
         <v>5001</v>
       </c>
       <c r="D61" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E61" t="s">
         <v>18</v>
@@ -3026,7 +2989,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" ht="17" spans="2:6">
+    <row r="62" spans="2:6">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -3034,12 +2997,12 @@
         <v>5001</v>
       </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E62" t="s">
         <v>18</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3119,10 +3082,10 @@
         <v>5001</v>
       </c>
       <c r="D67" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" t="s">
-        <v>18</v>
+        <v>38</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="F67" t="s">
         <v>88</v>
@@ -3136,7 +3099,7 @@
         <v>5001</v>
       </c>
       <c r="D68" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E68" t="s">
         <v>18</v>
@@ -3150,24 +3113,24 @@
         <v>65</v>
       </c>
       <c r="C69">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="D69" t="s">
         <v>38</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>44</v>
+      <c r="E69" t="s">
+        <v>18</v>
       </c>
       <c r="F69" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" ht="17" spans="2:6">
       <c r="B70" s="4">
         <v>66</v>
       </c>
       <c r="C70">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="D70" t="s">
         <v>38</v>
@@ -3175,8 +3138,8 @@
       <c r="E70" t="s">
         <v>18</v>
       </c>
-      <c r="F70" t="s">
-        <v>68</v>
+      <c r="F70" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -3184,16 +3147,16 @@
         <v>67</v>
       </c>
       <c r="C71">
-        <v>5002</v>
+        <v>6001</v>
       </c>
       <c r="D71" t="s">
-        <v>38</v>
-      </c>
-      <c r="E71" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" t="s">
-        <v>90</v>
+        <v>77</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="72" ht="17" spans="2:6">
@@ -3201,19 +3164,19 @@
         <v>68</v>
       </c>
       <c r="C72">
-        <v>5002</v>
+        <v>6001</v>
       </c>
       <c r="D72" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
         <v>18</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" ht="17" spans="2:6">
       <c r="B73" s="4">
         <v>69</v>
       </c>
@@ -3221,13 +3184,13 @@
         <v>6001</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>92</v>
+        <v>77</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="74" ht="17" spans="2:6">
@@ -3238,16 +3201,16 @@
         <v>6001</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E74" t="s">
         <v>18</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="75" ht="17" spans="2:6">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
       <c r="B75" s="4">
         <v>71</v>
       </c>
@@ -3255,16 +3218,16 @@
         <v>6001</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E75" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" ht="17" spans="2:6">
+      <c r="F75" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="4">
         <v>72</v>
       </c>
@@ -3272,13 +3235,13 @@
         <v>6001</v>
       </c>
       <c r="D76" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E76" t="s">
         <v>18</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>95</v>
+      <c r="F76" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="2:6">
@@ -3295,7 +3258,7 @@
         <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="2:6">
@@ -3312,7 +3275,7 @@
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="2:6">
@@ -3329,7 +3292,7 @@
         <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="2:6">
@@ -3340,13 +3303,13 @@
         <v>6001</v>
       </c>
       <c r="D80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" t="s">
-        <v>18</v>
+        <v>38</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="F80" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="2:6">
@@ -3354,16 +3317,16 @@
         <v>77</v>
       </c>
       <c r="C81">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="D81" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E81" t="s">
         <v>18</v>
       </c>
       <c r="F81" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="2:6">
@@ -3371,16 +3334,16 @@
         <v>78</v>
       </c>
       <c r="C82">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="D82" t="s">
         <v>38</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>44</v>
+      <c r="E82" t="s">
+        <v>18</v>
       </c>
       <c r="F82" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="2:6">
@@ -3388,7 +3351,7 @@
         <v>79</v>
       </c>
       <c r="C83">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="D83" t="s">
         <v>38</v>
@@ -3397,7 +3360,7 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="2:6">
@@ -3405,16 +3368,16 @@
         <v>80</v>
       </c>
       <c r="C84">
-        <v>6002</v>
+        <v>7001</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
-      </c>
-      <c r="E84" t="s">
-        <v>18</v>
+        <v>77</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F84" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="2:6">
@@ -3422,16 +3385,16 @@
         <v>81</v>
       </c>
       <c r="C85">
-        <v>6003</v>
+        <v>7001</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="E85" t="s">
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="2:6">
@@ -3442,13 +3405,13 @@
         <v>7001</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
       </c>
       <c r="F86" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="2:6">
@@ -3459,13 +3422,13 @@
         <v>7001</v>
       </c>
       <c r="D87" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="2:6">
@@ -3482,42 +3445,14 @@
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="4">
-        <v>85</v>
-      </c>
-      <c r="C89">
-        <v>7001</v>
-      </c>
-      <c r="D89" t="s">
-        <v>20</v>
-      </c>
-      <c r="E89" t="s">
-        <v>18</v>
-      </c>
-      <c r="F89" t="s">
-        <v>108</v>
-      </c>
+      <c r="C89" s="4"/>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="4">
-        <v>86</v>
-      </c>
-      <c r="C90">
-        <v>7001</v>
-      </c>
-      <c r="D90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E90" t="s">
-        <v>18</v>
-      </c>
-      <c r="F90" t="s">
-        <v>109</v>
-      </c>
+      <c r="C90" s="4"/>
     </row>
     <row r="91" spans="2:6">
       <c r="C91" s="4"/>
@@ -3529,10 +3464,10 @@
       <c r="C93" s="4"/>
     </row>
     <row r="94" spans="2:6">
-      <c r="C94" s="4"/>
+      <c r="B94" s="4"/>
     </row>
     <row r="95" spans="2:6">
-      <c r="C95" s="4"/>
+      <c r="B95" s="4"/>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="4"/>
@@ -3596,13 +3531,7 @@
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="4"/>
-    </row>
-    <row r="117" spans="2:6">
-      <c r="B117" s="4"/>
-    </row>
-    <row r="118" spans="2:6">
-      <c r="B118" s="4"/>
-      <c r="F118" s="6"/>
+      <c r="F116" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
